--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-09-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8269CE0-8E2D-4F4B-8104-1F34262E43CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C170CA6A-7816-445D-AC77-616E4B0BCE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32715" yWindow="915" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34665" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="387">
   <si>
     <t>SKU</t>
   </si>
@@ -796,15 +796,6 @@
     <t>£53.63</t>
   </si>
   <si>
-    <t>£71.04</t>
-  </si>
-  <si>
-    <t>£95.5</t>
-  </si>
-  <si>
-    <t>£84.22</t>
-  </si>
-  <si>
     <t>£78.5</t>
   </si>
   <si>
@@ -814,15 +805,6 @@
     <t>£79.95</t>
   </si>
   <si>
-    <t>£111.12</t>
-  </si>
-  <si>
-    <t>£153.89</t>
-  </si>
-  <si>
-    <t>£172.26</t>
-  </si>
-  <si>
     <t>£17.49</t>
   </si>
   <si>
@@ -1187,6 +1169,18 @@
   </si>
   <si>
     <t>£1338.99</t>
+  </si>
+  <si>
+    <t>£65.56</t>
+  </si>
+  <si>
+    <t>£1777.92</t>
+  </si>
+  <si>
+    <t>£2462.24</t>
+  </si>
+  <si>
+    <t>£2756.16</t>
   </si>
 </sst>
 </file>
@@ -1657,16 +1651,16 @@
         <v>240</v>
       </c>
       <c r="O2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="P2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="Q2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="R2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1713,16 +1707,16 @@
         <v>241</v>
       </c>
       <c r="O3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="P3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="R3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1754,7 +1748,7 @@
         <v>150</v>
       </c>
       <c r="J4" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K4" t="s">
         <v>189</v>
@@ -1769,16 +1763,16 @@
         <v>242</v>
       </c>
       <c r="O4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="P4" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="Q4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="R4" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1810,7 +1804,7 @@
         <v>151</v>
       </c>
       <c r="J5" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="K5" t="s">
         <v>190</v>
@@ -1825,16 +1819,16 @@
         <v>243</v>
       </c>
       <c r="O5" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="P5" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="Q5" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="R5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1884,13 +1878,13 @@
         <v>128</v>
       </c>
       <c r="P6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="Q6" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="R6" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1937,16 +1931,16 @@
         <v>245</v>
       </c>
       <c r="O7" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="P7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="Q7" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="R7" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1993,16 +1987,16 @@
         <v>246</v>
       </c>
       <c r="O8" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="P8" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="Q8" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="R8" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -2049,16 +2043,16 @@
         <v>247</v>
       </c>
       <c r="O9" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="P9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="Q9" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="R9" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -2105,16 +2099,16 @@
         <v>248</v>
       </c>
       <c r="O10" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="P10" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="Q10" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="R10" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -2143,10 +2137,10 @@
         <v>131</v>
       </c>
       <c r="I11" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="J11" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="K11" t="s">
         <v>195</v>
@@ -2161,16 +2155,16 @@
         <v>249</v>
       </c>
       <c r="O11" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="P11" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="Q11" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="R11" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -2217,16 +2211,16 @@
         <v>250</v>
       </c>
       <c r="O12" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="P12" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="Q12" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="R12" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -2258,7 +2252,7 @@
         <v>159</v>
       </c>
       <c r="J13" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="K13" t="s">
         <v>197</v>
@@ -2273,16 +2267,16 @@
         <v>251</v>
       </c>
       <c r="O13" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="P13" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="Q13" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="R13" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -2329,16 +2323,16 @@
         <v>252</v>
       </c>
       <c r="O14" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="P14" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="Q14" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="R14" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -2385,13 +2379,13 @@
         <v>253</v>
       </c>
       <c r="O15" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="P15" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Q15" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="R15" t="s">
         <v>100</v>
@@ -2426,7 +2420,7 @@
         <v>162</v>
       </c>
       <c r="J16" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K16" t="s">
         <v>200</v>
@@ -2441,16 +2435,16 @@
         <v>254</v>
       </c>
       <c r="O16" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="P16" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="Q16" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="R16" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2497,13 +2491,13 @@
         <v>255</v>
       </c>
       <c r="O17" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="P17" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q17" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="R17" t="s">
         <v>100</v>
@@ -2538,7 +2532,7 @@
         <v>164</v>
       </c>
       <c r="J18" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="K18" t="s">
         <v>202</v>
@@ -2553,16 +2547,16 @@
         <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="P18" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Q18" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="R18" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2582,7 +2576,7 @@
         <v>89</v>
       </c>
       <c r="F19" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -2594,7 +2588,7 @@
         <v>165</v>
       </c>
       <c r="J19" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="K19" t="s">
         <v>203</v>
@@ -2609,16 +2603,16 @@
         <v>257</v>
       </c>
       <c r="O19" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="P19" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="Q19" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="R19" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2638,7 +2632,7 @@
         <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G20" t="s">
         <v>119</v>
@@ -2650,7 +2644,7 @@
         <v>161</v>
       </c>
       <c r="J20" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="K20" t="s">
         <v>204</v>
@@ -2662,19 +2656,19 @@
         <v>230</v>
       </c>
       <c r="N20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O20" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="P20" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="Q20" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="R20" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2694,7 +2688,7 @@
         <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G21" t="s">
         <v>120</v>
@@ -2718,19 +2712,19 @@
         <v>231</v>
       </c>
       <c r="N21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="P21" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="Q21" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="R21" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2750,7 +2744,7 @@
         <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -2774,19 +2768,19 @@
         <v>232</v>
       </c>
       <c r="N22" t="s">
-        <v>260</v>
+        <v>383</v>
       </c>
       <c r="O22" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="P22" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Q22" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="R22" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2806,7 +2800,7 @@
         <v>93</v>
       </c>
       <c r="F23" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G23" t="s">
         <v>100</v>
@@ -2818,7 +2812,7 @@
         <v>167</v>
       </c>
       <c r="J23" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="K23" t="s">
         <v>207</v>
@@ -2830,19 +2824,19 @@
         <v>233</v>
       </c>
       <c r="N23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="O23" t="s">
         <v>93</v>
       </c>
       <c r="P23" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="Q23" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="R23" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2862,7 +2856,7 @@
         <v>94</v>
       </c>
       <c r="F24" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G24" t="s">
         <v>100</v>
@@ -2886,19 +2880,19 @@
         <v>234</v>
       </c>
       <c r="N24" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O24" t="s">
         <v>94</v>
       </c>
       <c r="P24" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="Q24" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="R24" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2930,7 +2924,7 @@
         <v>100</v>
       </c>
       <c r="J25" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="K25" t="s">
         <v>100</v>
@@ -2945,7 +2939,7 @@
         <v>157</v>
       </c>
       <c r="O25" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="P25" t="s">
         <v>100</v>
@@ -2974,7 +2968,7 @@
         <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G26" t="s">
         <v>100</v>
@@ -2998,19 +2992,19 @@
         <v>236</v>
       </c>
       <c r="N26" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="O26" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="P26" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="Q26" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="R26" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -3030,7 +3024,7 @@
         <v>97</v>
       </c>
       <c r="F27" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="G27" t="s">
         <v>100</v>
@@ -3054,19 +3048,19 @@
         <v>237</v>
       </c>
       <c r="N27" t="s">
-        <v>264</v>
+        <v>384</v>
       </c>
       <c r="O27" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="P27" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="Q27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="R27" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -3086,7 +3080,7 @@
         <v>98</v>
       </c>
       <c r="F28" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="G28" t="s">
         <v>100</v>
@@ -3110,19 +3104,19 @@
         <v>238</v>
       </c>
       <c r="N28" t="s">
-        <v>265</v>
+        <v>385</v>
       </c>
       <c r="O28" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="P28" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="Q28" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="R28" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3142,7 +3136,7 @@
         <v>99</v>
       </c>
       <c r="F29" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G29" t="s">
         <v>100</v>
@@ -3166,19 +3160,19 @@
         <v>239</v>
       </c>
       <c r="N29" t="s">
-        <v>266</v>
+        <v>386</v>
       </c>
       <c r="O29" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="Q29" t="s">
         <v>100</v>
       </c>
       <c r="R29" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
